--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_20/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_20/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>67.48</v>
+        <v>68.81</v>
       </c>
       <c r="D2" t="n">
-        <v>17.25</v>
+        <v>17.01</v>
       </c>
       <c r="E2" t="n">
-        <v>25.56</v>
+        <v>24.73</v>
       </c>
       <c r="F2" t="n">
-        <v>45.46</v>
+        <v>47.6</v>
       </c>
       <c r="G2" t="n">
-        <v>51.34</v>
+        <v>53.97</v>
       </c>
       <c r="H2" t="n">
-        <v>63.66</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>81.06</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>54.54</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>48.73</v>
+        <v>45.55</v>
       </c>
       <c r="D3" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="E3" t="n">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="F3" t="n">
-        <v>47.25</v>
+        <v>45.42</v>
       </c>
       <c r="G3" t="n">
-        <v>48.78</v>
+        <v>45.43</v>
       </c>
       <c r="H3" t="n">
-        <v>48.84</v>
+        <v>45.43</v>
       </c>
       <c r="I3" t="n">
-        <v>48.89</v>
+        <v>45.44</v>
       </c>
       <c r="J3" t="n">
-        <v>50</v>
+        <v>47.13</v>
       </c>
       <c r="K3" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.19</v>
+        <v>8.57</v>
       </c>
       <c r="D4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="E4" t="n">
-        <v>15.99</v>
+        <v>14.16</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>5.71</v>
       </c>
       <c r="G4" t="n">
-        <v>7.34</v>
+        <v>7.71</v>
       </c>
       <c r="H4" t="n">
-        <v>8.460000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>9.34</v>
+        <v>9.57</v>
       </c>
       <c r="J4" t="n">
-        <v>9.56</v>
+        <v>9.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.56</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>157.99</v>
+        <v>162.61</v>
       </c>
       <c r="D5" t="n">
-        <v>19.01</v>
+        <v>28.21</v>
       </c>
       <c r="E5" t="n">
-        <v>12.03</v>
+        <v>17.35</v>
       </c>
       <c r="F5" t="n">
-        <v>112.37</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>141.88</v>
+        <v>156.66</v>
       </c>
       <c r="H5" t="n">
-        <v>155.88</v>
+        <v>171.87</v>
       </c>
       <c r="I5" t="n">
-        <v>176.32</v>
+        <v>177.26</v>
       </c>
       <c r="J5" t="n">
-        <v>197.41</v>
+        <v>199.8</v>
       </c>
       <c r="K5" t="n">
-        <v>85.04000000000001</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>30.97</v>
+        <v>17.63</v>
       </c>
       <c r="F6" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>4.42</v>
+        <v>2.97</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>3.99</v>
       </c>
       <c r="K6" t="n">
-        <v>2.96</v>
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>
